--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104513_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104513_W7.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2159</v>
+        <v>5.209</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5773</v>
+        <v>5.3451</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3615</v>
+        <v>-0.1362</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8065</v>
+        <v>-0.8351</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1424</v>
+        <v>-1.1703</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3359</v>
+        <v>0.3351</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7005</v>
+        <v>1.6405</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7944</v>
+        <v>-0.8391</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4948</v>
+        <v>2.4795</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.507</v>
+        <v>-2.4756</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9297</v>
+        <v>0.9546</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5989</v>
+        <v>0.4363</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3309</v>
+        <v>0.5184</v>
       </c>
       <c r="V2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6562</v>
+        <v>4.1919</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1757</v>
+        <v>2.533</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4805</v>
+        <v>1.659</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8757</v>
+        <v>2.2871</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7632</v>
+        <v>4.7075</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.6389</v>
+        <v>-2.4204</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0176</v>
+        <v>2.9851</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2295</v>
+        <v>4.3782</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.2471</v>
+        <v>-1.3931</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1419</v>
+        <v>-0.6979</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5337</v>
+        <v>0.3294</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-1.0273</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6926</v>
+        <v>0.6772</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7652</v>
+        <v>0.1414</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4577</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0246</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5237</v>
+        <v>3.2931</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3066</v>
+        <v>0.409</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2172</v>
+        <v>2.8841</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2857</v>
+        <v>-0.8723</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7113</v>
+        <v>1.7689</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.4256</v>
+        <v>-2.6412</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0123</v>
+        <v>-1.0334</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3985</v>
+        <v>1.2238</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3861</v>
+        <v>-2.2572</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7266</v>
+        <v>0.1611</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3129</v>
+        <v>0.5451</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0395</v>
+        <v>-0.384</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0112</v>
+        <v>0.3232</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1179</v>
+        <v>-0.5089</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1291</v>
+        <v>0.832</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>2.0212</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0567</v>
+        <v>1.6345</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2636</v>
+        <v>0.8407</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7931</v>
+        <v>0.7938</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4191</v>
+        <v>-0.4145</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9452</v>
+        <v>1.9417</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.3643</v>
+        <v>-2.3562</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4511</v>
+        <v>1.431</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0882</v>
+        <v>2.0717</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8702</v>
+        <v>-1.8455</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6365</v>
+        <v>1.2068</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9467</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6899</v>
+        <v>0.6589</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1347</v>
+        <v>0.4492</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2397</v>
+        <v>-0.9028</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3744</v>
+        <v>1.352</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2633</v>
+        <v>0.5235</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4531</v>
+        <v>0.5427</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8103</v>
+        <v>-0.0193</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2261</v>
+        <v>0.6233</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1141</v>
+        <v>0.5861</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4894</v>
+        <v>-0.0998</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5672</v>
+        <v>-0.0433</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9222</v>
+        <v>-0.0565</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4661</v>
+        <v>-0.2532</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8026</v>
+        <v>-0.1116</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6636</v>
+        <v>-0.1416</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.2664</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1938</v>
+        <v>-1.006</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2783</v>
+        <v>1.2724</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5198</v>
+        <v>-1.2563</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5411</v>
+        <v>-0.4538</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0213</v>
+        <v>-0.8026</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6261</v>
+        <v>0.2184</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5888</v>
+        <v>0.1067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.1117</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1063</v>
+        <v>-1.4747</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0477</v>
+        <v>-0.5604</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0586</v>
+        <v>-0.9143</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6206</v>
+        <v>1.591</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4174</v>
+        <v>1.0519</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2032</v>
+        <v>0.5391</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>0.387</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8101</v>
+        <v>-0.8253</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1755</v>
+        <v>-2.4309</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3655</v>
+        <v>1.6055</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8235</v>
+        <v>-1.8401</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1006</v>
+        <v>-2.1159</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2645</v>
+        <v>-1.2957</v>
       </c>
       <c r="K8" t="n">
-        <v>0.876</v>
+        <v>0.8651</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.1406</v>
+        <v>-2.1608</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5444</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7601</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8771</v>
+        <v>0.6663</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1171</v>
+        <v>0.1013</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5535</v>
+        <v>-1.2545</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005</v>
+        <v>-2.9578</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5585</v>
+        <v>1.7032</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6038</v>
+        <v>-1.2957</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1212</v>
+        <v>-0.0606</v>
       </c>
       <c r="I9" t="n">
-        <v>0.725</v>
+        <v>-1.2352</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2088</v>
+        <v>-0.7834</v>
       </c>
       <c r="K9" t="n">
-        <v>0.052</v>
+        <v>-0.0452</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1568</v>
+        <v>-0.7382</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.605</v>
+        <v>-0.5124</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1732</v>
+        <v>-0.0154</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4318</v>
+        <v>-0.497</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-3.6421</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1573</v>
+        <v>0.6331</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>0.3782</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0877</v>
+        <v>0.2548</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0339</v>
+        <v>-1.4347</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4755</v>
+        <v>0.1166</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4416</v>
+        <v>-1.5513</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2939</v>
+        <v>0.6048</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.065</v>
+        <v>-0.1207</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2289</v>
+        <v>0.7255</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7514</v>
+        <v>1.2061</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0315</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7198</v>
+        <v>1.1543</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5425</v>
+        <v>-0.6012</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0335</v>
+        <v>-0.1724</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.509</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1503</v>
+        <v>-0.0395</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1875</v>
+        <v>0.0487</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0372</v>
+        <v>-0.0882</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7712</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1756</v>
+        <v>-2.7111</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3622</v>
+        <v>-3.3084</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8134</v>
+        <v>0.5972</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8143</v>
+        <v>-3.0479</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4922</v>
+        <v>-0.3452</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3221</v>
+        <v>-2.7027</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5836</v>
+        <v>-2.0747</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1385</v>
+        <v>0.0862</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4451</v>
+        <v>-2.1608</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.398</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6308</v>
+        <v>-0.4314</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7672</v>
+        <v>-0.5419</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4119</v>
+        <v>0.3368</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2299</v>
+        <v>0.1321</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1821</v>
+        <v>0.2047</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3539</v>
+        <v>-3.0351</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1802</v>
+        <v>-0.1896</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8263</v>
+        <v>-2.8455</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0448</v>
+        <v>-1.8015</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3551</v>
+        <v>-0.4803</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6896</v>
+        <v>-1.3213</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.054</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0866</v>
+        <v>0.1379</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1406</v>
+        <v>0.4392</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9908</v>
+        <v>-2.3786</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4417</v>
+        <v>-0.6182</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.549</v>
+        <v>-1.7604</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3091</v>
+        <v>0.5389</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>0.4202</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4561</v>
+        <v>0.1187</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.744700000000002</v>
+        <v>5.7834</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2987</v>
+        <v>-1.551099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>7.0435</v>
+        <v>7.334200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.931800000000001</v>
+        <v>-7.948</v>
       </c>
       <c r="H13" t="n">
-        <v>6.608899999999998</v>
+        <v>6.6057</v>
       </c>
       <c r="I13" t="n">
-        <v>-14.5407</v>
+        <v>-14.5542</v>
       </c>
       <c r="J13" t="n">
-        <v>3.721</v>
+        <v>3.4943</v>
       </c>
       <c r="K13" t="n">
-        <v>8.746300000000003</v>
+        <v>8.623099999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.025300000000001</v>
+        <v>-5.128900000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.6529</v>
+        <v>-11.4423</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1376</v>
+        <v>-2.0171</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.5153</v>
+        <v>-9.4253</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0001000000000003221</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.1467</v>
+        <v>-18.2105</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1466</v>
+        <v>18.2106</v>
       </c>
       <c r="S13" t="n">
-        <v>5.670800000000001</v>
+        <v>6.7365</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1324</v>
+        <v>3.2025</v>
       </c>
       <c r="U13" t="n">
-        <v>3.5386</v>
+        <v>3.5339</v>
       </c>
       <c r="V13" t="n">
-        <v>7.0057</v>
+        <v>6.9952</v>
       </c>
       <c r="W13" t="n">
-        <v>9.994800000000001</v>
+        <v>9.962999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.9889</v>
+        <v>-2.9677</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2777</v>
+        <v>4.366</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0116</v>
+        <v>2.574</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2661</v>
+        <v>1.7921</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4738</v>
+        <v>3.4754</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3275</v>
+        <v>2.3237</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1462</v>
+        <v>1.1517</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3877</v>
+        <v>3.3737</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7534</v>
+        <v>2.7407</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M14" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1018</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5091</v>
+        <v>0.5947</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6635</v>
+        <v>0.2505</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8456</v>
+        <v>0.3441</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8612</v>
+        <v>2.3351</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5074</v>
+        <v>3.947</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6462</v>
+        <v>-1.6118</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0647</v>
+        <v>4.0588</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7648</v>
+        <v>0.764</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2999</v>
+        <v>3.2948</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5409</v>
+        <v>4.5162</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2224</v>
+        <v>1.2098</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3185</v>
+        <v>3.3064</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4762</v>
+        <v>-0.4574</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4718</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7652</v>
+        <v>-0.2929</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2934</v>
+        <v>0.2929</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0695</v>
+        <v>1.4485</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6855</v>
+        <v>-1.3697</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7551</v>
+        <v>2.8181</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2474</v>
+        <v>2.2475</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4474</v>
+        <v>-0.4426</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6948</v>
+        <v>2.69</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4409</v>
+        <v>2.4179</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3565</v>
+        <v>0.348</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0843</v>
+        <v>2.0699</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1935</v>
+        <v>-0.1704</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R16" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8169</v>
+        <v>-0.4332</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0434</v>
+        <v>-0.6902</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2265</v>
+        <v>0.257</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5552</v>
+        <v>1.0844</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2006</v>
+        <v>1.3823</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6454</v>
+        <v>-0.2979</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4128</v>
+        <v>3.405</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8643</v>
+        <v>1.8667</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5486</v>
+        <v>1.5383</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2408</v>
+        <v>3.2015</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0304</v>
+        <v>3.0164</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2104</v>
+        <v>0.1851</v>
       </c>
       <c r="M17" t="n">
-        <v>0.172</v>
+        <v>0.2035</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3382</v>
+        <v>1.3532</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5647</v>
+        <v>-2.0231</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0253</v>
+        <v>-0.7901</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5395</v>
+        <v>-1.233</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4653</v>
+        <v>-0.1908</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0224</v>
+        <v>-1.4281</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4877</v>
+        <v>1.2373</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4862</v>
+        <v>-0.5622</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1876</v>
+        <v>-4.7956</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2985</v>
+        <v>4.2334</v>
       </c>
       <c r="J18" t="n">
-        <v>0.092</v>
+        <v>-0.4659</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>-3.4591</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>2.9932</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.0963</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.205</v>
+        <v>-1.3365</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3732</v>
+        <v>1.2402</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>3.1868</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>3.4145</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.206</v>
+        <v>-1.1812</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>-0.7346</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1364</v>
+        <v>-0.4466</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BURJANADZE</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1624</v>
+        <v>-0.3112</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7358</v>
+        <v>0.1405</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5734</v>
+        <v>-0.4516</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2737</v>
+        <v>-0.4819</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.482</v>
+        <v>-0.184</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7917</v>
+        <v>-0.2979</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8315</v>
+        <v>0.0917</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3708</v>
+        <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4608</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5578</v>
+        <v>-0.5736</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1113</v>
+        <v>-0.2012</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6691</v>
+        <v>-0.3724</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3424</v>
+        <v>-0.0569</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2299</v>
+        <v>0.0487</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5722</v>
+        <v>-0.1057</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>B. BURJANADZE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2389</v>
+        <v>-1.3306</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0814</v>
+        <v>-2.9866</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8425</v>
+        <v>1.6559</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5462</v>
+        <v>-1.268</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.7817</v>
+        <v>-0.477</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2355</v>
+        <v>-0.791</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.412</v>
+        <v>-1.8435</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.4265</v>
+        <v>-0.376</v>
       </c>
       <c r="L20" t="n">
-        <v>3.0145</v>
+        <v>-1.4676</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1343</v>
+        <v>0.5755</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3552</v>
+        <v>-0.1011</v>
       </c>
       <c r="O20" t="n">
-        <v>1.221</v>
+        <v>0.6766</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1757</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>3.4025</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2293</v>
+        <v>-0.5179</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4426</v>
+        <v>-0.0049</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7867</v>
+        <v>-0.513</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5526</v>
+        <v>-3.047</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.597</v>
+        <v>-2.8627</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0445</v>
+        <v>-0.1842</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2383</v>
+        <v>-0.2364</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4804</v>
+        <v>-1.4819</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2422</v>
+        <v>1.2455</v>
       </c>
       <c r="J21" t="n">
-        <v>0.627</v>
+        <v>0.6078</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3779</v>
+        <v>-0.3899</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0048</v>
+        <v>0.9977</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8653</v>
+        <v>-0.8442</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1809</v>
+        <v>-0.3066</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1785</v>
+        <v>-0.0561</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0024</v>
+        <v>-0.2505</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4709</v>
+        <v>-3.0659</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5015</v>
+        <v>-3.1656</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0306</v>
+        <v>0.0998</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7452</v>
+        <v>-0.7207</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0087</v>
+        <v>-1.9995</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2636</v>
+        <v>1.2788</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0722</v>
+        <v>-0.0781</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9651</v>
+        <v>0.9809</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3401</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0948</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2453</v>
+        <v>-0.2168</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6184</v>
+        <v>-6.0265</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1841</v>
+        <v>-3.5654</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4343</v>
+        <v>-2.4611</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9774</v>
+        <v>-1.9693</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1774</v>
+        <v>-2.1798</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.2105</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3608</v>
+        <v>-0.3791</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3359</v>
+        <v>0.3351</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6166</v>
+        <v>-1.5902</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3895</v>
+        <v>-0.8084</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1693</v>
+        <v>-0.523</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2202</v>
+        <v>-0.2854</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.744899999999999</v>
+        <v>-4.738</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.043299999999999</v>
+        <v>-7.334299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>2.298599999999999</v>
+        <v>2.5966</v>
       </c>
       <c r="G24" t="n">
-        <v>7.9317</v>
+        <v>7.9482</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.608600000000001</v>
+        <v>-6.606000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>14.5406</v>
+        <v>14.5541</v>
       </c>
       <c r="J24" t="n">
-        <v>11.6528</v>
+        <v>11.4422</v>
       </c>
       <c r="K24" t="n">
-        <v>2.137300000000001</v>
+        <v>2.0169</v>
       </c>
       <c r="L24" t="n">
-        <v>9.5151</v>
+        <v>9.4252</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.7211</v>
+        <v>-3.4939</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.7463</v>
+        <v>-8.6229</v>
       </c>
       <c r="O24" t="n">
-        <v>5.0253</v>
+        <v>5.128800000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-3.33066907387547e-16</v>
       </c>
       <c r="Q24" t="n">
-        <v>-18.1466</v>
+        <v>-18.2105</v>
       </c>
       <c r="R24" t="n">
-        <v>18.1466</v>
+        <v>18.2106</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.6707</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.5383</v>
+        <v>-3.534000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.132400000000001</v>
+        <v>-2.157</v>
       </c>
       <c r="V24" t="n">
-        <v>-7.0059</v>
+        <v>-6.995200000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9889</v>
+        <v>2.9677</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.9948</v>
+        <v>-9.963000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104513_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104513_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-2.9677</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104513_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.963000000000001</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
